--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A7FDD-3600-4F5D-9A71-2FC758386E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05626FC-DC2F-4DD8-A911-D5EEC2F0E3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 19-12-2025'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05626FC-DC2F-4DD8-A911-D5EEC2F0E3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DD4A3-5607-43A8-901F-84E56F0FB794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 02-02-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DD4A3-5607-43A8-901F-84E56F0FB794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4617AD8D-0E40-4F7D-82AC-49D5656665E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 02-02-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 20-02-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4617AD8D-0E40-4F7D-82AC-49D5656665E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A4FE84-DA9E-41F4-BD84-FF6EB0C6CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 20-02-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 04-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A4FE84-DA9E-41F4-BD84-FF6EB0C6CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE961D06-27EE-4933-9235-3678A0D3A0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 04-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 06-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE961D06-27EE-4933-9235-3678A0D3A0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414F29AE-9F69-421A-AFD2-8B33BD8E4BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414F29AE-9F69-421A-AFD2-8B33BD8E4BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B2FBD1-2F81-4EDD-8FD1-3492CFC7CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B2FBD1-2F81-4EDD-8FD1-3492CFC7CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0885729-9028-46CE-AB59-B93FB6C20C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 06-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 09-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0885729-9028-46CE-AB59-B93FB6C20C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E8A14F-3B76-41C6-B4F8-FA3928B64AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E8A14F-3B76-41C6-B4F8-FA3928B64AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E723DD4-908A-45E2-990C-8A3B00C710EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 09-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 11-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E723DD4-908A-45E2-990C-8A3B00C710EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F73C0-73C2-4C84-9B6E-669ECE4C00CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F73C0-73C2-4C84-9B6E-669ECE4C00CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D25629-4229-45A4-841B-315AB194D554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 11-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 20-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D25629-4229-45A4-841B-315AB194D554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCA233A-33E5-443F-B2AE-068010F0D387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 20-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 25-03-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCA233A-33E5-443F-B2AE-068010F0D387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D1C7A3-01E5-4047-9901-CD0137DBBE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 25-03-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 08-04-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D1C7A3-01E5-4047-9901-CD0137DBBE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0786F8-EB53-499E-A779-132CAC268ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 08-04-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 10-04-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0786F8-EB53-499E-A779-132CAC268ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE0C5AF-E6CD-4F52-A3F5-A7F3B4414216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE0C5AF-E6CD-4F52-A3F5-A7F3B4414216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A96D9-815D-4838-8D2C-44A82DD8DBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 10-04-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 14-04-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A96D9-815D-4838-8D2C-44A82DD8DBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FC0643-E2D4-4018-A6AC-DBBA7E9304F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 14-04-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 24-04-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FC0643-E2D4-4018-A6AC-DBBA7E9304F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81212B-88D8-4D39-8CD8-9468524422F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81212B-88D8-4D39-8CD8-9468524422F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4D443C-1A54-486C-91C3-29341514DC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 24-04-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 27-04-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4D443C-1A54-486C-91C3-29341514DC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C900C1E-8C50-49E5-8809-A889623D81B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 27-04-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 06-05-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C900C1E-8C50-49E5-8809-A889623D81B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8D96E9-41A5-471C-A82C-70A9B46B9C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 06-05-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 01-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8D96E9-41A5-471C-A82C-70A9B46B9C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FD777A-0CD0-451D-8C31-F4FBBF0EE73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 01-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 02-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FD777A-0CD0-451D-8C31-F4FBBF0EE73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4908CB98-74B5-4F37-8216-51BC50BC3687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4908CB98-74B5-4F37-8216-51BC50BC3687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B4375B-360D-4EDE-A751-27F1A5015E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 02-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 05-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05626FC-DC2F-4DD8-A911-D5EEC2F0E3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C06443B-62BB-4022-A6BB-E7585BA58C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C06443B-62BB-4022-A6BB-E7585BA58C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5330758-974F-4F27-8C5F-D6052130D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 09-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5330758-974F-4F27-8C5F-D6052130D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8868437D-FE22-4FF5-89D6-AF135CC97BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8868437D-FE22-4FF5-89D6-AF135CC97BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC20D52-1C80-4BAF-BFA2-57738DFBED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC20D52-1C80-4BAF-BFA2-57738DFBED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9F655C-A186-4245-BB1A-921387648F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 09-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 15-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9F655C-A186-4245-BB1A-921387648F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321444F-EB4B-4A76-843B-355E8FD4FE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 15-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321444F-EB4B-4A76-843B-355E8FD4FE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD132FC-FA67-44FE-A23E-DF1D6D2EA29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD132FC-FA67-44FE-A23E-DF1D6D2EA29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B04617B-BC0E-48E9-840D-EDB210FB6AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321444F-EB4B-4A76-843B-355E8FD4FE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3139D2DE-88A3-4948-8C62-CD69AA707B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3139D2DE-88A3-4948-8C62-CD69AA707B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6C04B8-05F0-407D-BBEE-B16C7B63643A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 25-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6C04B8-05F0-407D-BBEE-B16C7B63643A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D9A307-893B-4E3E-B935-3DD38F12533B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 25-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 30-06-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D9A307-893B-4E3E-B935-3DD38F12533B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459D5944-576B-47F3-B301-AA1948BC471E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459D5944-576B-47F3-B301-AA1948BC471E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65118D3-90BB-41AA-B5BC-4D640EC10147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 30-06-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65118D3-90BB-41AA-B5BC-4D640EC10147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B97CC03-C3C7-483C-92CB-D4AB220C5AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 02-07-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65118D3-90BB-41AA-B5BC-4D640EC10147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF8C1A3-52F5-470C-8768-0CB4273EAA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B97CC03-C3C7-483C-92CB-D4AB220C5AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3831D85-244A-4BD3-89CF-2A239CF4E70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 02-07-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3831D85-244A-4BD3-89CF-2A239CF4E70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E0CE05-03EE-41D0-99D7-FFAE70F6EBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 09-07-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E0CE05-03EE-41D0-99D7-FFAE70F6EBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93C20D3-1FCF-43FE-8C86-E006883039DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 09-07-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 19-08-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93C20D3-1FCF-43FE-8C86-E006883039DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF28694-082D-4C2E-B826-17136AAD8498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 19-08-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 21-08-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF28694-082D-4C2E-B826-17136AAD8498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34BF894-EBFB-4992-AB6B-DB1679EFB6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 21-08-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 27-08-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34BF894-EBFB-4992-AB6B-DB1679EFB6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A893F3-192A-4DC3-A8BE-5C466CBFF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 27-08-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 02-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A893F3-192A-4DC3-A8BE-5C466CBFF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB327B5E-A164-4428-A081-ECD2B5112CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 02-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 06-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB327B5E-A164-4428-A081-ECD2B5112CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698A0E01-A214-4BE5-A1F7-DE9B9A628711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698A0E01-A214-4BE5-A1F7-DE9B9A628711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAAD8DA-B62E-46C9-A841-7A2537FCF976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 06-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 07-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAAD8DA-B62E-46C9-A841-7A2537FCF976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4ADFC5-EA30-4FD2-878F-8BED33BD2EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 07-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 09-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4ADFC5-EA30-4FD2-878F-8BED33BD2EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D307B6-8FF3-4EE0-8E36-C61AE2745BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
